--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4031,57 +4031,55 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136007050</v>
+        <v>137534791</v>
       </c>
       <c r="B32" t="n">
-        <v>58167</v>
+        <v>57224</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Klittmyrarna, Dlr</t>
+          <t>Hykjeberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457953</v>
+        <v>457759</v>
       </c>
       <c r="R32" t="n">
-        <v>6792218</v>
+        <v>6792666</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4105,22 +4103,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,52 +4133,56 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Per Ax</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Per Ax</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007050</t>
+          <t>https://artportalen.se/Sighting/137534791</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135942946</v>
+        <v>136007050</v>
       </c>
       <c r="B33" t="n">
-        <v>58627</v>
+        <v>58167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103041</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -4192,13 +4194,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458272</v>
+        <v>457953</v>
       </c>
       <c r="R33" t="n">
-        <v>6792433</v>
+        <v>6792218</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,22 +4224,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,27 +4254,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942946</t>
+          <t>https://artportalen.se/Sighting/136007050</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135942934</v>
+        <v>135942946</v>
       </c>
       <c r="B34" t="n">
-        <v>8463</v>
+        <v>58627</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,27 +4282,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4309,13 +4311,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458408</v>
+        <v>458272</v>
       </c>
       <c r="R34" t="n">
-        <v>6792311</v>
+        <v>6792433</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,13 +4382,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942934</t>
+          <t>https://artportalen.se/Sighting/135942946</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135942937</v>
+        <v>135942934</v>
       </c>
       <c r="B35" t="n">
         <v>8463</v>
@@ -4426,13 +4428,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458418</v>
+        <v>458408</v>
       </c>
       <c r="R35" t="n">
-        <v>6792258</v>
+        <v>6792311</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4461,7 +4463,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4473,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,13 +4499,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942937</t>
+          <t>https://artportalen.se/Sighting/135942934</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135942944</v>
+        <v>135942937</v>
       </c>
       <c r="B36" t="n">
         <v>8463</v>
@@ -4543,13 +4545,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458301</v>
+        <v>458418</v>
       </c>
       <c r="R36" t="n">
-        <v>6792433</v>
+        <v>6792258</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4578,7 +4580,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4590,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,26 +4601,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4634,13 +4616,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942944</t>
+          <t>https://artportalen.se/Sighting/135942937</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135945185</v>
+        <v>135942944</v>
       </c>
       <c r="B37" t="n">
         <v>8463</v>
@@ -4680,13 +4662,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458265</v>
+        <v>458301</v>
       </c>
       <c r="R37" t="n">
-        <v>6792434</v>
+        <v>6792433</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4715,7 +4697,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4725,7 +4707,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4737,6 +4719,16 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM37" t="inlineStr">
         <is>
           <t>Stående död trädstam/högstubbe</t>
@@ -4744,65 +4736,61 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945185</t>
+          <t>https://artportalen.se/Sighting/135942944</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135942942</v>
+        <v>135945185</v>
       </c>
       <c r="B38" t="n">
-        <v>99342</v>
+        <v>8463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,13 +4799,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458309</v>
+        <v>458265</v>
       </c>
       <c r="R38" t="n">
-        <v>6792448</v>
+        <v>6792434</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4846,7 +4834,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4844,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4867,28 +4855,38 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942942</t>
+          <t>https://artportalen.se/Sighting/135945185</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135945182</v>
+        <v>135942942</v>
       </c>
       <c r="B39" t="n">
         <v>99342</v>
@@ -4918,7 +4916,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4932,13 +4930,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458307</v>
+        <v>458309</v>
       </c>
       <c r="R39" t="n">
-        <v>6792449</v>
+        <v>6792448</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4967,7 +4965,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4977,7 +4975,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4992,65 +4990,74 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945182</t>
+          <t>https://artportalen.se/Sighting/135942942</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131033123</v>
+        <v>135945182</v>
       </c>
       <c r="B40" t="n">
-        <v>79085</v>
+        <v>99342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457734</v>
+        <v>458307</v>
       </c>
       <c r="R40" t="n">
-        <v>6792504</v>
+        <v>6792449</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5074,12 +5081,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5094,27 +5111,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033123</t>
+          <t>https://artportalen.se/Sighting/135945182</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135445420</v>
+        <v>131033123</v>
       </c>
       <c r="B41" t="n">
-        <v>79201</v>
+        <v>79085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,19 +5157,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hykjeberg, Dlr</t>
+          <t>Hykjeberg söder, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457768</v>
+        <v>457734</v>
       </c>
       <c r="R41" t="n">
-        <v>6792314</v>
+        <v>6792504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5179,12 +5193,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,23 +5207,128 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033123</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135445420</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hykjeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>457768</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6792314</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445420</t>
         </is>
@@ -5257,6 +5376,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
